--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_1502.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_1502.xlsx
@@ -1624,6 +1624,9 @@
       <c r="E20" t="n">
         <v>1</v>
       </c>
+      <c r="H20" t="n">
+        <v>0.7</v>
+      </c>
       <c r="I20" t="n">
         <v>0.84</v>
       </c>
@@ -1639,12 +1642,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: CHEX@HEX, THDMAJ_A@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: CHEX@HEX, THDMAJ_A@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 1502-08-08-FG (PARTcommunity / CADENAS, CHEX@HEX=C, THDMAJ_A@DRIVE=A1THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 1502-08-08-FG (PARTcommunity / CADENAS, CHEX@HEX=C, THDMAJ_A@DRIVE=A1THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
